--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486787_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486787_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2224</v>
+        <v>1.3562</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9776</v>
+        <v>1.1362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2448</v>
+        <v>0.22</v>
       </c>
       <c r="G2" t="n">
         <v>2.5219</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.651</v>
+        <v>-0.5172</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6347</v>
+        <v>-0.476</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0163</v>
+        <v>-0.0411</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.758</v>
+        <v>0.9095</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.229</v>
+        <v>-0.705</v>
       </c>
       <c r="F3" t="n">
-        <v>1.987</v>
+        <v>1.6145</v>
       </c>
       <c r="G3" t="n">
         <v>0.17</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1929</v>
+        <v>-0.0413</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8279</v>
+        <v>-0.3038</v>
       </c>
       <c r="U3" t="n">
-        <v>0.635</v>
+        <v>0.2625</v>
       </c>
       <c r="V3" t="n">
         <v>0.008500000000000001</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3291</v>
+        <v>0.3841</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9777</v>
+        <v>0.1215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6485</v>
+        <v>0.2627</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3643</v>
+        <v>-0.1763</v>
       </c>
       <c r="H4" t="n">
-        <v>0.414</v>
+        <v>-1.4898</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0497</v>
+        <v>1.3135</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3106</v>
+        <v>0.5766</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7944</v>
+        <v>-0.0406</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4837</v>
+        <v>0.6172</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9464</v>
+        <v>-0.753</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3804</v>
+        <v>-1.4492</v>
       </c>
       <c r="O4" t="n">
-        <v>0.434</v>
+        <v>0.6962</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.7031</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.02</v>
+        <v>-2.1239</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7156</v>
+        <v>-0.0965</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8749</v>
+        <v>0.441</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1593</v>
+        <v>-0.5375</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2941</v>
+        <v>1.2362</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8568</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5627</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6113</v>
+        <v>-0.5923</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3416</v>
+        <v>0.4981</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2697</v>
+        <v>-1.0904</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3353</v>
+        <v>0.6076</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5178</v>
+        <v>-0.4143</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8175</v>
+        <v>1.0219</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.479</v>
+        <v>2.1809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0347</v>
+        <v>1.0346</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.5138</v>
+        <v>1.1462</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1437</v>
+        <v>-1.5733</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5525</v>
+        <v>-1.4489</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6962</v>
+        <v>-0.1244</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7377</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q5" t="n">
+        <v>-2.1239</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.2345</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.6756</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.7377</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.0223</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.9097</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.9320000000000001</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7771</v>
+        <v>-0.7408</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8163</v>
+        <v>-0.6449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0392</v>
+        <v>-0.0959</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1763</v>
+        <v>-2.3353</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4898</v>
+        <v>-0.5178</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3135</v>
+        <v>-1.8175</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5766</v>
+        <v>-2.479</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0406</v>
+        <v>0.0347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6172</v>
+        <v>-2.5138</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.753</v>
+        <v>0.1437</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4492</v>
+        <v>-0.5525</v>
       </c>
       <c r="O6" t="n">
         <v>0.6962</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2577</v>
+        <v>-0.1518</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4968</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.761</v>
+        <v>-0.7582</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2362</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008500000000000001</v>
+        <v>-1.2192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8213</v>
+        <v>-0.8568</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4429</v>
+        <v>-0.8878</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2642</v>
+        <v>0.031</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6076</v>
+        <v>0.5527</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4143</v>
+        <v>-0.7245</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0219</v>
+        <v>1.2773</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1809</v>
+        <v>1.3672</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0346</v>
+        <v>0.1035</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1462</v>
+        <v>1.2637</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5733</v>
+        <v>-0.8145</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4489</v>
+        <v>-0.828</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1244</v>
+        <v>0.0135</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1239</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4635</v>
+        <v>0.0345</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3859</v>
+        <v>-0.1312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8494</v>
+        <v>0.1657</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0733</v>
+        <v>-0.8607</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2533</v>
+        <v>-1.7569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.18</v>
+        <v>0.8962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5527</v>
+        <v>-1.1393</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7245</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2773</v>
+        <v>-0.3323</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3672</v>
+        <v>-1.2769</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1035</v>
+        <v>-0.6688</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2637</v>
+        <v>-0.6081</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8145</v>
+        <v>0.1376</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.828</v>
+        <v>-0.1382</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0135</v>
+        <v>0.2758</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1819</v>
+        <v>0.3792</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4966</v>
+        <v>0.1998</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3147</v>
+        <v>0.1794</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>0.2856</v>
       </c>
       <c r="W8" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1958</v>
+        <v>-1.3</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0671</v>
+        <v>-1.6163</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8714</v>
+        <v>0.3163</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1393</v>
+        <v>-1.2308</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-1.545</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3323</v>
+        <v>0.3142</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2769</v>
+        <v>-0.761</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6688</v>
+        <v>-0.9237</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6081</v>
+        <v>0.1628</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1376</v>
+        <v>-0.4698</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1382</v>
+        <v>-0.6212</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2758</v>
+        <v>0.1514</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5792</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0441</v>
+        <v>0.193</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1105</v>
+        <v>0.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1546</v>
+        <v>0.083</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4049</v>
+        <v>-1.4214</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6715</v>
+        <v>-0.8098</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2666</v>
+        <v>-0.6116</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2308</v>
+        <v>1.1479</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.545</v>
+        <v>-1.366</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3142</v>
+        <v>2.5139</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.761</v>
+        <v>1.3488</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9237</v>
+        <v>-0.6067</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1628</v>
+        <v>1.9555</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4698</v>
+        <v>-0.2009</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6212</v>
+        <v>-0.7593</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1514</v>
+        <v>0.5583</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.1239</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.9654</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.9308</v>
-      </c>
       <c r="S10" t="n">
-        <v>0.0882</v>
+        <v>-0.8481</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0548</v>
+        <v>-0.0347</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0333</v>
+        <v>-0.8134</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2277</v>
+        <v>-0.5627</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>-0.5627</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.445</v>
+        <v>-1.7275</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6099</v>
+        <v>-2.0532</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8351</v>
+        <v>0.3257</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1479</v>
+        <v>0.3643</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.366</v>
+        <v>0.414</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5139</v>
+        <v>-0.0497</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3488</v>
+        <v>1.3106</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6067</v>
+        <v>1.7944</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9555</v>
+        <v>-0.4837</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2009</v>
+        <v>-0.9464</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7593</v>
+        <v>-1.3804</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5583</v>
+        <v>0.434</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1585</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1239</v>
+        <v>-5.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8717</v>
+        <v>0.3172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1652</v>
+        <v>0.7994</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0369</v>
+        <v>-0.4821</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5627</v>
+        <v>0.2941</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X11" t="n">
         <v>-0.5627</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6774</v>
+        <v>-4.8497</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5459</v>
+        <v>-6.7181</v>
       </c>
       <c r="F12" t="n">
         <v>1.8685</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4826999999999999</v>
+        <v>0.4826999999999994</v>
       </c>
       <c r="H12" t="n">
         <v>-7.588200000000001</v>
@@ -1363,16 +1363,16 @@
         <v>8.0709</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1814</v>
+        <v>4.181399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3404</v>
+        <v>-0.3404000000000003</v>
       </c>
       <c r="L12" t="n">
         <v>4.521800000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.698899999999999</v>
+        <v>-3.6989</v>
       </c>
       <c r="N12" t="n">
         <v>-7.2476</v>
@@ -1390,10 +1390,10 @@
         <v>14.4808</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7931</v>
+        <v>-0.9654999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8240000000000001</v>
+        <v>1.652</v>
       </c>
       <c r="U12" t="n">
         <v>-2.6173</v>
@@ -1405,7 +1405,7 @@
         <v>4.8255</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.2963</v>
+        <v>-6.296299999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5009</v>
+        <v>5.5973</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1645</v>
+        <v>3.4748</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3364</v>
+        <v>2.1226</v>
       </c>
       <c r="G13" t="n">
         <v>3.5534</v>
@@ -1468,13 +1468,13 @@
         <v>3.2823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4966</v>
+        <v>0.5999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3305</v>
+        <v>0.6408</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.0409</v>
       </c>
       <c r="V13" t="n">
         <v>0.2856</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6549</v>
+        <v>3.2122</v>
       </c>
       <c r="E14" t="n">
-        <v>1.001</v>
+        <v>1.524</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6539</v>
+        <v>1.6882</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8945</v>
+        <v>0.385</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3866</v>
+        <v>3.1996</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4921</v>
+        <v>-2.8145</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0614</v>
+        <v>1.3591</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3183</v>
+        <v>2.8555</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2569</v>
+        <v>-1.4965</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.167</v>
+        <v>-0.974</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0682</v>
+        <v>0.344</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2352</v>
+        <v>-1.3181</v>
       </c>
       <c r="P14" t="n">
+        <v>2.7031</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1931</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.8962</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="V14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-3.0892</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.0892</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.5174</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.3305</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.1869</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.243</v>
-      </c>
       <c r="W14" t="n">
-        <v>2.6984</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5986</v>
+        <v>2.2892</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6966</v>
+        <v>1.1045</v>
       </c>
       <c r="F15" t="n">
-        <v>0.902</v>
+        <v>1.1847</v>
       </c>
       <c r="G15" t="n">
-        <v>0.385</v>
+        <v>0.8945</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1996</v>
+        <v>2.3866</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.8145</v>
+        <v>-1.4921</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3591</v>
+        <v>1.0614</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8555</v>
+        <v>2.3183</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4965</v>
+        <v>-1.2569</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.974</v>
+        <v>-0.167</v>
       </c>
       <c r="N15" t="n">
-        <v>0.344</v>
+        <v>0.0682</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3181</v>
+        <v>-0.2352</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7031</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>-3.0892</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8962</v>
+        <v>3.0892</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4895</v>
+        <v>1.1517</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4693</v>
+        <v>0.4339</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0202</v>
+        <v>0.7178</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.6984</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5528</v>
+        <v>1.0044</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4118</v>
+        <v>-2.1334</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9645</v>
+        <v>3.1378</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9944</v>
+        <v>-1.2384</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.696</v>
+        <v>1.7389</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2985</v>
+        <v>-2.9773</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.614</v>
+        <v>-0.5334</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6953</v>
+        <v>1.5328</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>-2.0662</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3805</v>
+        <v>-0.705</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2061</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3799</v>
+        <v>-0.9111</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-3.0892</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3169</v>
+        <v>3.0892</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8408</v>
+        <v>0.3586</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8127</v>
+        <v>0.2616</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0281</v>
+        <v>0.097</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2856</v>
+        <v>1.8842</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0161</v>
+        <v>0.2853</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7539</v>
+        <v>0.6512</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7378</v>
+        <v>-0.3659</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2384</v>
+        <v>0.8094</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7389</v>
+        <v>0.8275</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9773</v>
+        <v>-0.0181</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5334</v>
+        <v>1.6857</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5328</v>
+        <v>1.0346</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0662</v>
+        <v>0.6511</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.705</v>
+        <v>-0.8763</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2061</v>
+        <v>-0.2071</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9111</v>
+        <v>-0.6692</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1379</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.06909999999999999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.0689</v>
+      </c>
+      <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-3.0892</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.0892</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.6619</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.359</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.3029</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.8842</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1836</v>
+        <v>-0.1572</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4444</v>
+        <v>-2.2734</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6279</v>
+        <v>2.1162</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8094</v>
+        <v>-0.9944</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8275</v>
+        <v>-0.696</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0181</v>
+        <v>-0.2985</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6857</v>
+        <v>-0.614</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0346</v>
+        <v>-0.6953</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6511</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8763</v>
+        <v>-0.3805</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2071</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6692</v>
+        <v>-0.3799</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6068</v>
+        <v>1.1308</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2759</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3309</v>
+        <v>0.1797</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1817</v>
+        <v>-2.0397</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.505</v>
+        <v>-1.4016</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6767</v>
+        <v>-0.6381</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4493</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2097</v>
+        <v>0.3517</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0554</v>
+        <v>0.048</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2651</v>
+        <v>0.3037</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9421</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2485</v>
+        <v>-2.4457</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5044</v>
+        <v>-2.8147</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2559</v>
+        <v>0.369</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4428</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>0.48</v>
+        <v>0.2828</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3032</v>
+        <v>-0.0071</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1768</v>
+        <v>0.2898</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2856</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>5.677299999999998</v>
+        <v>7.745799999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8686</v>
+        <v>-1.868600000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>7.5459</v>
+        <v>9.6145</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4826000000000006</v>
+        <v>-0.4826000000000001</v>
       </c>
       <c r="H21" t="n">
         <v>7.5883</v>
@@ -2077,7 +2077,7 @@
         <v>-4.1815</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3402999999999999</v>
+        <v>0.3403</v>
       </c>
       <c r="O21" t="n">
         <v>-4.5219</v>
@@ -2092,19 +2092,19 @@
         <v>17.3769</v>
       </c>
       <c r="S21" t="n">
-        <v>1.793100000000001</v>
+        <v>3.8616</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6173</v>
+        <v>2.6172</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8241999999999998</v>
+        <v>1.2442</v>
       </c>
       <c r="V21" t="n">
         <v>1.4707</v>
       </c>
       <c r="W21" t="n">
-        <v>6.296200000000001</v>
+        <v>6.2962</v>
       </c>
       <c r="X21" t="n">
         <v>-4.8255</v>
